--- a/outputs/marketing/auditoria/Faixa_Etaria.xlsx
+++ b/outputs/marketing/auditoria/Faixa_Etaria.xlsx
@@ -27661,10 +27661,10 @@
         </is>
       </c>
       <c r="L356" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="N356" s="2" t="inlineStr">
         <is>
@@ -35337,10 +35337,10 @@
         </is>
       </c>
       <c r="L457" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M457" s="3" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="N457" s="3" t="inlineStr">
         <is>
@@ -45901,10 +45901,10 @@
         </is>
       </c>
       <c r="L596" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="N596" s="2" t="inlineStr">
         <is>
@@ -46053,10 +46053,10 @@
         </is>
       </c>
       <c r="L598" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="N598" s="2" t="inlineStr">
         <is>
